--- a/pastoral-projects/values-in-action/downloads/Values_in_Action_Tracker.xlsx
+++ b/pastoral-projects/values-in-action/downloads/Values_in_Action_Tracker.xlsx
@@ -63,7 +63,7 @@
   </si>
   <si>
     <t xml:space="preserve">How to use this tracker
-• Type each student’s name into column A once, in the same order across all three sheets.
+• Type each student’s name into column A of all three sheets, in the same order.
 • Fill in their role model and two values here, and choose their Track from the dropdown.
 • Then log their evidence on the matching sheet: Daily Practice Log or Lasting Change Log.
 • A one-week window is the default. Stretch it if your form needs longer, especially for Lasting Change.</t>
